--- a/data/CReDEs/v4/dg_rcbc.xlsx
+++ b/data/CReDEs/v4/dg_rcbc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9257F8-D5DF-49B4-95F3-4CDAC9A7F0DE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC9AC91-08DD-4392-A386-53EE226C39AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{37E406E1-D7B5-4F4C-B658-5EFA45CFD28B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="179021" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -232,7 +232,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写以下选项：无，有，未描述,</t>
+    <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/data/CReDEs/v4/dg_rcbc.xlsx
+++ b/data/CReDEs/v4/dg_rcbc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC9AC91-08DD-4392-A386-53EE226C39AB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A3EE88-346A-4F16-94BF-79D0E31AD8BE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{37E406E1-D7B5-4F4C-B658-5EFA45CFD28B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021" concurrentCalc="0"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -204,10 +204,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写以下选项：无，有，未描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>检查方式</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -233,6 +229,10 @@
   </si>
   <si>
     <t>请填写以下选项：无，有，未描述，若有则填写相应的内容，单位为“个”</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：无，轻，中，重，未查，未描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -815,7 +815,7 @@
         <v>38</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="H7" s="3"/>
     </row>
@@ -836,7 +836,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H8" s="3"/>
     </row>
@@ -857,7 +857,7 @@
         <v>38</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H9" s="3"/>
     </row>
@@ -872,13 +872,13 @@
         <v>26</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H10" s="3"/>
     </row>
@@ -899,7 +899,7 @@
         <v>16</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11" s="3"/>
     </row>
@@ -917,10 +917,10 @@
         <v>32</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="H12" s="3"/>
     </row>
@@ -953,13 +953,13 @@
         <v>37</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>38</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H14" s="3"/>
     </row>
